--- a/artfynd/A 34996-2025 artfynd.xlsx
+++ b/artfynd/A 34996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108289111</v>
+        <v>108288996</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>486025.5729741338</v>
+        <v>485937</v>
       </c>
       <c r="R2" t="n">
-        <v>6728199.755942476</v>
+        <v>6728241</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +780,226 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108861519</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Dammskog, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485945</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6728253</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Andreas Öster, Lina Lejonberg, Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108289111</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hålldammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>486026</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6728199</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34996-2025 artfynd.xlsx
+++ b/artfynd/A 34996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108288996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108861519</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108289111</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>